--- a/zy72088/ml_threshold_calibrator/output/demo_anomalies_latest.xlsx
+++ b/zy72088/ml_threshold_calibrator/output/demo_anomalies_latest.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="26">
   <si>
     <t>指标名称</t>
   </si>
@@ -37,6 +37,9 @@
     <t>证据链接</t>
   </si>
   <si>
+    <t>用户注册转化率</t>
+  </si>
+  <si>
     <t>DAU日活用户</t>
   </si>
   <si>
@@ -49,19 +52,37 @@
     <t>投诉率</t>
   </si>
   <si>
+    <t>新用户7日留存</t>
+  </si>
+  <si>
+    <t>需人工确认</t>
+  </si>
+  <si>
     <t>参数冲突待裁决</t>
   </si>
   <si>
     <t>样本越界</t>
   </si>
   <si>
-    <t>参数表与导入数据阈值冲突，请人工裁决</t>
-  </si>
-  <si>
-    <t>样本值 4.5 高于当前阈值 3.0; 样本值 5.2 超出当前阈值 3.0 的150%</t>
-  </si>
-  <si>
-    <t>样本值 0.025 超出当前阈值 0.015 的150%</t>
+    <t>样本值 0.052 高于当前阈值 0.05; 样本值 0.051 高于当前阈值 0.05</t>
+  </si>
+  <si>
+    <t>样本值 102000.0 高于当前阈值 100000.0; 样本值 105000.0 高于当前阈值 100000.0; 参数表与导入数据阈值冲突，请人工裁决</t>
+  </si>
+  <si>
+    <t>样本值 155.0 高于当前阈值 150.0; 样本值 152.0 高于当前阈值 150.0; 样本值 160.0 高于当前阈值 150.0</t>
+  </si>
+  <si>
+    <t>样本值 3.2 高于当前阈值 3.0; 样本值 4.5 高于当前阈值 3.0; 样本值 5.2 超出当前阈值 3.0 的150%</t>
+  </si>
+  <si>
+    <t>样本值 0.018 高于当前阈值 0.015; 样本值 0.025 超出当前阈值 0.015 的150%</t>
+  </si>
+  <si>
+    <t>样本值 0.42 高于当前阈值 0.4</t>
+  </si>
+  <si>
+    <t>1. 查看样本分布；2. 根据业务容忍度选择阈值；3. 在参数表中确认并标记人工调整</t>
   </si>
   <si>
     <t>1. 核对参数表和导入数据的来源；2. 确认业务口径；3. 在参数表中更新最终值</t>
@@ -428,7 +449,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -459,19 +480,22 @@
         <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C2">
-        <v>100000</v>
+        <v>0.05</v>
+      </c>
+      <c r="D2">
+        <v>0.05</v>
       </c>
       <c r="E2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="G2" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -479,19 +503,19 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C3">
-        <v>150</v>
+        <v>100000</v>
       </c>
       <c r="E3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F3" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="G3" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -499,22 +523,22 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C4">
-        <v>3</v>
+        <v>150</v>
       </c>
       <c r="D4">
-        <v>5.17</v>
+        <v>159</v>
       </c>
       <c r="E4" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F4" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="G4" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -522,22 +546,68 @@
         <v>10</v>
       </c>
       <c r="B5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5">
+        <v>3</v>
+      </c>
+      <c r="D5">
+        <v>5.17</v>
+      </c>
+      <c r="E5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6">
+        <v>0.015</v>
+      </c>
+      <c r="D6">
+        <v>0.015</v>
+      </c>
+      <c r="E6" t="s">
+        <v>20</v>
+      </c>
+      <c r="F6" t="s">
+        <v>24</v>
+      </c>
+      <c r="G6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" t="s">
         <v>12</v>
       </c>
-      <c r="C5">
-        <v>0.015</v>
-      </c>
-      <c r="D5">
-        <v>0.015</v>
-      </c>
-      <c r="E5" t="s">
-        <v>15</v>
-      </c>
-      <c r="F5" t="s">
-        <v>17</v>
-      </c>
-      <c r="G5" t="s">
-        <v>18</v>
+      <c r="B7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7">
+        <v>0.4</v>
+      </c>
+      <c r="D7">
+        <v>0.4</v>
+      </c>
+      <c r="E7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G7" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
